--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T06:07:01+00:00</t>
+    <t>2024-10-25T08:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:29:24+00:00</t>
+    <t>2024-10-29T09:40:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,13 +451,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>CoverageEligibilityRequest.extension:ExtensionDays</t>
-  </si>
-  <si>
-    <t>ExtensionDays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-extensionDays}
+    <t>CoverageEligibilityRequest.extension:verlängerungstage</t>
+  </si>
+  <si>
+    <t>verlängerungstage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verlaengerungstage}
 </t>
   </si>
   <si>
@@ -467,13 +467,13 @@
     <t>"Verlaengerungstage:"Anzahl der Verlaengerungstage bei Verlaengerung.</t>
   </si>
   <si>
-    <t>CoverageEligibilityRequest.extension:PremiumClass</t>
-  </si>
-  <si>
-    <t>PremiumClass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-PremiumClass}
+    <t>CoverageEligibilityRequest.extension:sonderklasse</t>
+  </si>
+  <si>
+    <t>sonderklasse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-sonderklasse}
 </t>
   </si>
   <si>
@@ -1491,7 +1491,7 @@
   <cols>
     <col min="1" max="1" width="56.875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="56.875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.4296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:40:57+00:00</t>
+    <t>2024-10-29T10:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
